--- a/output/pdf_financials_xlsx/SRL.xlsx
+++ b/output/pdf_financials_xlsx/SRL.xlsx
@@ -5965,7 +5965,7 @@
         <v>5.284786</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0.095669</v>
+        <v>0.458314</v>
       </c>
       <c r="P91" s="3" t="n">
         <v>0.962973</v>
@@ -5990,49 +5990,49 @@
         <v>2.684491</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3.624364</v>
+        <v>2.691043</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.392949</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.24224</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.24224</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.24224</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.337221</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.127221</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.127221</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.187221</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.823385</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.797803</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.668238</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.961306</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.265236</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.86348</v>
       </c>
     </row>
     <row r="93">
@@ -7474,13 +7474,13 @@
         <v>-0.427623</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>1.565614</v>
+        <v>0.8877620000000001</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-1.67804</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-2.952952</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>0.193685</v>
@@ -9911,7 +9911,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -15854,7 +15858,11 @@
           <t>Currency translation reserve - - - 362,645</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -23809,7 +23817,11 @@
           <t>Share-based payments reserve 4,392,949</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -31989,7 +32001,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -32672,7 +32688,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SRL.xlsx
+++ b/output/pdf_financials_xlsx/SRL.xlsx
@@ -1044,40 +1044,40 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002867</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.004341</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000373</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.01332</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.040174</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.098187</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.031189</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.022291</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.067124</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.067235</v>
       </c>
     </row>
     <row r="13">
@@ -2084,40 +2084,40 @@
         <v>-2.099525</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.660175</v>
+        <v>-1.663042</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.227182</v>
+        <v>-1.231523</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.811907</v>
+        <v>-2.81228</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-1.172674</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.55633</v>
+        <v>-1.56965</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.307194</v>
+        <v>1.26702</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.320363</v>
+        <v>-1.41855</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.997462</v>
+        <v>-1.028651</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>2.727621</v>
+        <v>2.70533</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-3.904786</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.675322</v>
+        <v>-5.742446</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-5.532616</v>
+        <v>-5.599851</v>
       </c>
     </row>
     <row r="28">
@@ -2200,40 +2200,40 @@
         <v>-2.015295</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.562641</v>
+        <v>-1.565508</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.155723</v>
+        <v>-1.160064</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.707377</v>
+        <v>-2.70775</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-1.105673</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.483953</v>
+        <v>-1.497273</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.469816</v>
+        <v>1.429642</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.173642</v>
+        <v>-1.271829</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.850639</v>
+        <v>-0.8818279999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.923286</v>
+        <v>2.900995</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-3.693074</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.496247</v>
+        <v>-5.563371</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-5.415944</v>
+        <v>-5.483179</v>
       </c>
     </row>
     <row r="30">
@@ -2501,34 +2501,34 @@
         <v>5.915058</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>7.048245</v>
+        <v>0.679719</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.128253</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.177745</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.049236</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.043249</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.64061</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.764062</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.784301</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.079065</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.345851</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>3.721815</v>
@@ -2617,34 +2617,34 @@
         <v>5.915058</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>7.048245</v>
+        <v>0.679719</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.128253</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.177745</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.049236</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.043249</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.64061</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.764062</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.784301</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.079065</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.345851</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>3.721815</v>
@@ -3313,34 +3313,34 @@
         <v>0.013712</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>0.122733</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.289353</v>
+        <v>0.1611</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.230499</v>
+        <v>0.052754</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.109641</v>
+        <v>0.060405</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.109619</v>
+        <v>0.06637</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.677311</v>
+        <v>0.036701</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.559133</v>
+        <v>0.795071</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>7.028185</v>
+        <v>4.243884</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.073112</v>
+        <v>0.994047</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.814006</v>
+        <v>2.468155</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>1.215707</v>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -20943,7 +20943,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -41246,7 +41246,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -52718,7 +52718,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">

--- a/output/pdf_financials_xlsx/SRL.xlsx
+++ b/output/pdf_financials_xlsx/SRL.xlsx
@@ -6479,25 +6479,25 @@
         <v>0.045607</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.003782</v>
+        <v>0.01667</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.005591</v>
+        <v>0.005966</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.005161</v>
+        <v>0.0031</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>-0.001021</v>
+        <v>0.002814</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-0.007099</v>
+        <v>-0.008554000000000001</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>-0.096389</v>
+        <v>-0.109644</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>-0.136286</v>
+        <v>-0.125914</v>
       </c>
       <c r="M101" s="3" t="n">
         <v>-0.080746</v>
@@ -6778,16 +6778,16 @@
         <v>0.225009</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.768757</v>
+        <v>0.7725919999999999</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.734728</v>
+        <v>-0.736183</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.260865</v>
+        <v>0.24761</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.596599</v>
+        <v>0.606971</v>
       </c>
       <c r="M106" s="3" t="n">
         <v>-1.032834</v>
@@ -7312,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>3.223404</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -30203,7 +30203,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -31213,7 +31217,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -33492,7 +33500,11 @@
           <t>(Increase) decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -34583,7 +34595,11 @@
           <t>Decrease in GST receivable</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
